--- a/data/trans_orig/IP2003-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Edad-trans_orig.xlsx
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18169</t>
+          <t>16774</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16832</t>
+          <t>16800</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15076</t>
+          <t>16304</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>31318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>234460</t>
+          <t>235855</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245742</t>
+          <t>245957</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236199</t>
+          <t>236231</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>246495</t>
+          <t>246453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>475254</t>
+          <t>474342</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>490584</t>
+          <t>489356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27602</t>
+          <t>26832</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>43160</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>23548</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39480</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>27,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55232</t>
+          <t>54938</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>77758</t>
+          <t>78289</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>29,19%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83120</t>
+          <t>84388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99946</t>
+          <t>100716</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101222</t>
+          <t>101561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>117665</t>
+          <t>117154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>72,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190492</t>
+          <t>189961</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>213018</t>
+          <t>213312</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,41%</t>
+          <t>79,52%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57291</t>
+          <t>56113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>77860</t>
+          <t>77588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,11%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46153</t>
+          <t>47014</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>67080</t>
+          <t>66720</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109047</t>
+          <t>108881</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>138462</t>
+          <t>137613</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>116237</t>
+          <t>116509</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136806</t>
+          <t>137984</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,89%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>71,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138969</t>
+          <t>139329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159896</t>
+          <t>159035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>67,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>261684</t>
+          <t>262533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291099</t>
+          <t>291265</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,61%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>98898</t>
+          <t>98461</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>129850</t>
+          <t>130729</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>83875</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>112638</t>
+          <t>112949</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190643</t>
+          <t>190555</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>232740</t>
+          <t>231108</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>515190</t>
+          <t>514311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>546142</t>
+          <t>546579</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>79,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>572252</t>
+          <t>571941</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>600322</t>
+          <t>601015</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1097190</t>
+          <t>1098822</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139287</t>
+          <t>1139375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5966</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>9286</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22341</t>
+          <t>22342</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18476</t>
+          <t>18009</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35295</t>
+          <t>36339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>218974</t>
+          <t>218759</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230284</t>
+          <t>230332</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246650</t>
+          <t>246649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>259574</t>
+          <t>259705</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>469946</t>
+          <t>468902</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>486765</t>
+          <t>487232</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35707</t>
+          <t>34866</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53408</t>
+          <t>54033</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>24096</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40375</t>
+          <t>40511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63873</t>
+          <t>64271</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88407</t>
+          <t>87134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103635</t>
+          <t>103010</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121336</t>
+          <t>122177</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118196</t>
+          <t>118060</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>134353</t>
+          <t>134475</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>227207</t>
+          <t>228480</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251741</t>
+          <t>251343</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,99%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,76%</t>
+          <t>79,64%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46074</t>
+          <t>47116</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66973</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37902</t>
+          <t>37124</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>55899</t>
+          <t>56041</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89125</t>
+          <t>89090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117184</t>
+          <t>117439</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103755</t>
+          <t>104097</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124654</t>
+          <t>123612</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>124056</t>
+          <t>123914</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>142053</t>
+          <t>142831</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233499</t>
+          <t>233244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261558</t>
+          <t>261593</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,59%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96409</t>
+          <t>96632</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>127193</t>
+          <t>128679</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>79780</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109947</t>
+          <t>109427</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182712</t>
+          <t>182534</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225701</t>
+          <t>225112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,48%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>535698</t>
+          <t>534212</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>566482</t>
+          <t>566259</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>593493</t>
+          <t>594013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>624305</t>
+          <t>623660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1140630</t>
+          <t>1141219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183619</t>
+          <t>1183797</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>7128</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18179</t>
+          <t>18343</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6668</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18181</t>
+          <t>17964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16799</t>
+          <t>16919</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33798</t>
+          <t>32875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>191644</t>
+          <t>191480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>202774</t>
+          <t>202695</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>239880</t>
+          <t>240097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>251828</t>
+          <t>251393</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>434086</t>
+          <t>435009</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451085</t>
+          <t>450965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,38%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44263</t>
+          <t>42216</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28132</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45173</t>
+          <t>46187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59120</t>
+          <t>57234</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83512</t>
+          <t>82565</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144636</t>
+          <t>146683</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>162649</t>
+          <t>162967</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>143399</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>160440</t>
+          <t>160268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>293959</t>
+          <t>294906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318351</t>
+          <t>320237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,88%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,34%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>35440</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53488</t>
+          <t>55321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33526</t>
+          <t>33454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53313</t>
+          <t>52888</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72845</t>
+          <t>73582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99387</t>
+          <t>101414</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>118485</t>
+          <t>116652</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>137084</t>
+          <t>136533</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>120735</t>
+          <t>121160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>140522</t>
+          <t>140594</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>246633</t>
+          <t>244606</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273175</t>
+          <t>272438</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,95%</t>
+          <t>78,73%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>74365</t>
+          <t>73987</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>103934</t>
+          <t>105283</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>78067</t>
+          <t>77560</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>108202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160639</t>
+          <t>158663</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>202155</t>
+          <t>200926</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>554621</t>
+          <t>553272</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>584190</t>
+          <t>584568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>592921</t>
+          <t>592693</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>622828</t>
+          <t>623335</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1157294</t>
+          <t>1158523</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1198810</t>
+          <t>1200786</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,33%</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41770</t>
+          <t>43315</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,7 +6757,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>90199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6976</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>15213</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30779</t>
+          <t>31449</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141933</t>
+          <t>142279</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>152832</t>
+          <t>152949</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162563</t>
+          <t>162271</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174587</t>
+          <t>174592</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309920</t>
+          <t>309250</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325161</t>
+          <t>325486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>21281</t>
+          <t>22153</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35331</t>
+          <t>35360</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43473</t>
+          <t>43235</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70574</t>
+          <t>71012</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>131272</t>
+          <t>130286</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>151791</t>
+          <t>150919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177159</t>
+          <t>177130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195886</t>
+          <t>195229</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314989</t>
+          <t>314551</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342090</t>
+          <t>342328</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,79%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>47160</t>
+          <t>46097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>133316</t>
+          <t>135755</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50383</t>
+          <t>50057</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97030</t>
+          <t>99170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108661</t>
+          <t>106503</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220863</t>
+          <t>211929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>36,48%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>142142</t>
+          <t>139703</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>228298</t>
+          <t>229361</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>208453</t>
+          <t>206313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255100</t>
+          <t>255426</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>360077</t>
+          <t>369011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>472279</t>
+          <t>474437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,67%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83378</t>
+          <t>85095</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>192532</t>
+          <t>196712</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>85121</t>
+          <t>84499</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138824</t>
+          <t>142608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>181128</t>
+          <t>180719</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>298933</t>
+          <t>303305</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,61%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463539</t>
+          <t>459359</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>572693</t>
+          <t>570976</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>608641</t>
+          <t>604857</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662344</t>
+          <t>662966</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1104603</t>
+          <t>1100231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1222408</t>
+          <t>1222817</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP2003-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP2003-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -836,47 +836,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>70767</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>85108</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70767</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>85108</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10735</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6561</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17287</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,24%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,83%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11288</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6672</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16774</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7151</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>18040</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,64%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,64%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>10735</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6578</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>16800</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,24%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>15756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31318</t>
+          <t>30593</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>365</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>242296</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>235744</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>246470</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,76%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,17%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>361</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>241341</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>235855</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>245957</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>234589</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>245478</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>93,36%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,36%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>365</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>242296</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>236231</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>246453</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,76%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>474342</t>
+          <t>475067</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>489356</t>
+          <t>489904</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253031</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>378</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>252629</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>252629</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>252629</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253031</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30533</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22975</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>38989</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,7%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>27,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>35135</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26832</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>43160</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27658</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>44179</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,55%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,84%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>30533</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>23548</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39141</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54938</t>
+          <t>54251</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78289</t>
+          <t>76849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>110169</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>101713</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>117727</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,3%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>72,29%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>92413</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>84388</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100716</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>83369</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>99890</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>72,45%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>66,16%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>78,96%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>110169</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>101561</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>117154</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,3%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>189961</t>
+          <t>191401</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>213312</t>
+          <t>213999</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>70,81%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,78%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>140702</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>140702</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>140702</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>140702</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>140702</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>140702</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>56267</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>46791</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>66269</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,31%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22,71%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>66882</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>56113</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>77588</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>56085</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>76383</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>34,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>28,91%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>56267</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>47014</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>66720</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,31%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>108881</t>
+          <t>106930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>137613</t>
+          <t>137650</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>149782</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>139780</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>159258</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>72,69%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>67,84%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>77,29%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>127215</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>116509</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>137984</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>117714</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>138012</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>65,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>71,09%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>149782</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>139329</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>159035</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>72,69%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262533</t>
+          <t>262496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>291265</t>
+          <t>293216</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>97535</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>83687</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>111819</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>16,33%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>113305</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>98461</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>130729</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>97996</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>128552</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,57%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>15,26%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>97535</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>83875</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>112949</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>190555</t>
+          <t>189962</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>231108</t>
+          <t>232012</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>587355</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>573071</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>601203</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>85,76%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>83,67%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>794</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>531735</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>514311</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>546579</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>516488</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>547044</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>82,43%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>84,74%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>587355</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>571941</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>601015</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>85,76%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1098822</t>
+          <t>1097918</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1139375</t>
+          <t>1139968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1030</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>684890</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>684890</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>684890</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>963</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>645040</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1030</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>684890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2783,47 +2783,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>95923</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>98870</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>95923</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>14840</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>9599</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>23534</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10823</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5918</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>17491</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6078</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16707</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,58%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,5%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>14840</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>9286</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>22342</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18009</t>
+          <t>18493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36339</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>354</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>254151</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>245457</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>259392</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>91,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>225427</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>218759</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>230332</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>219543</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>230172</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,42%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,5%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>354</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>254151</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>246649</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>259705</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>94,48%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>468902</t>
+          <t>470096</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>487232</t>
+          <t>486748</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31754</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>24101</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>39957</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,2%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>43766</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34866</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54033</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35447</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>54652</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,41%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>31754</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>24096</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>40511</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>20,02%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64271</t>
+          <t>64438</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87134</t>
+          <t>87841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,83%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>126817</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>118614</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>134470</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>79,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,8%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>113277</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>103010</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>122177</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102391</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>121596</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>65,59%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,8%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>126817</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>118060</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>134475</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>79,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>228480</t>
+          <t>227773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>251343</t>
+          <t>251176</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,58%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46203</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37214</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55646</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>25,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20,68%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>56642</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47116</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66631</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>46988</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>66758</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>33,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39,03%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>46203</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37124</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56041</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89090</t>
+          <t>88629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>117439</t>
+          <t>116832</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>133752</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124309</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>142741</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>74,33%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,32%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>114086</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>104097</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>123612</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>103970</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>123740</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>66,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>60,97%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>133752</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>123914</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>142831</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>74,33%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>72,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>233244</t>
+          <t>233851</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261593</t>
+          <t>262054</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,73%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>170728</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>92797</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>79432</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>108594</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,29%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,44%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>111231</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>96632</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>128679</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>95300</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>127320</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>16,78%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,41%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>92797</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>79780</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>109427</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182534</t>
+          <t>181667</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>225112</t>
+          <t>225261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>610643</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>594846</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>624008</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,56%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,71%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>796</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>551660</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>534212</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>566259</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>535571</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>567591</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>83,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,59%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>610643</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>594013</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>623660</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>86,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1141219</t>
+          <t>1141070</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1183797</t>
+          <t>1184664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>703440</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>703440</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>703440</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>954</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>662891</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>703440</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>703440</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>703440</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4730,47 +4730,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>80214</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>87859</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>80214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11627</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6438</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18504</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,51%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11888</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>7128</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>18343</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>7066</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>19113</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,67%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>11627</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>6668</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>17964</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16517</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>364</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>246434</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>239557</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>251623</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,49%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>314</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>197935</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>191480</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>202695</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>190710</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>202757</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,33%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,6%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>364</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>246434</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>240097</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>251393</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,49%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>435009</t>
+          <t>436376</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>450965</t>
+          <t>451367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>331</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>209823</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>36439</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28615</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>46701</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>19,32%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>24,77%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>33428</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>25932</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42216</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>25064</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42399</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,7%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>22,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>36439</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>28304</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>46187</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>19,32%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>57234</t>
+          <t>57435</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>82565</t>
+          <t>83539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>152133</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>141871</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159957</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>80,68%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>75,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>155471</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>146683</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>162967</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>146500</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>163835</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,3%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>77,65%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>86,27%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>152133</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>142385</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>160268</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>80,68%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>294906</t>
+          <t>293932</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320237</t>
+          <t>320036</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,78%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42836</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33184</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>51869</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,61%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,8%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43639</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35440</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55321</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34763</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>54257</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,38%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>32,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>42836</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>33454</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>52888</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,61%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>73582</t>
+          <t>73980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101414</t>
+          <t>101822</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>131212</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>122179</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>140864</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>75,39%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70,2%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>180</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>128334</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>116652</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>136533</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>117716</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>137210</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>74,62%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>67,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>79,39%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>131212</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>121160</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>140594</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>75,39%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>68,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>244606</t>
+          <t>244198</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>272438</t>
+          <t>272040</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,62%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>244</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171973</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171973</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171973</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>90901</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>77447</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>106142</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>12,97%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,05%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,14%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>88955</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>73987</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>105283</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>73998</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>103586</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>13,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>15,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>90901</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>77560</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>108202</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158663</t>
+          <t>159691</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>200926</t>
+          <t>201619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,83%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>609994</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>594753</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>623448</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>87,03%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>84,86%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,95%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>860</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>569600</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>553272</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>584568</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>554969</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>584557</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>86,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>84,01%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>88,77%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>874</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>609994</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>592693</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>623335</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1158523</t>
+          <t>1157830</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1200786</t>
+          <t>1199758</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,25%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700895</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>988</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>658555</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>658555</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>658555</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>700895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,107 +6564,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4614</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>9,63%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6135</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -6677,74 +6677,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39284</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>37668</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,01%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>44563</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>46812</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>43315</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>47929</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,67%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>90,37%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>175</t>
@@ -6752,27 +6752,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>95217</t>
+          <t>83847</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90199</t>
+          <t>82303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>39676</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>48405</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47929</t>
+          <t>44563</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96334</t>
+          <t>84239</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>10485</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6193</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>16939</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3,95%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>10612</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16857</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,67%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,59%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>16982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>20976</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15213</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>31449</t>
+          <t>29721</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,85%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>146259</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>139805</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>150551</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,31%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,19%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>96,05%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>148524</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>142279</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>152949</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,11%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>169580</t>
+          <t>134534</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>162271</t>
+          <t>128043</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>174592</t>
+          <t>139112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>318104</t>
+          <t>280793</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309250</t>
+          <t>272048</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>325486</t>
+          <t>287291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156744</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>257</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159136</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181563</t>
+          <t>145025</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>340699</t>
+          <t>301769</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21935</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>14026</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>30856</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,96%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>15,42%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>30227</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>22153</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>42786</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,72%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24905</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35360</t>
+          <t>37579</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>55133</t>
+          <t>50028</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>43235</t>
+          <t>38359</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71012</t>
+          <t>62157</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>178191</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>169270</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>186100</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>89,04%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>84,58%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>92,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>142845</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>130286</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>150919</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>82,53%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,28%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>87,2%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>187585</t>
+          <t>146579</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>177130</t>
+          <t>137093</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>195229</t>
+          <t>154644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>78,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>330430</t>
+          <t>324770</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>314551</t>
+          <t>312641</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>342328</t>
+          <t>336439</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>62099</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>87827</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21,22%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>16,49%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>30,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>72209</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>46097</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>135755</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>26,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>16,73%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>67359</t>
+          <t>48996</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>50057</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>99170</t>
+          <t>61776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>139568</t>
+          <t>111095</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>106503</t>
+          <t>92102</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>211929</t>
+          <t>138749</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>230546</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>204818</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>244388</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>78,78%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>69,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>83,51%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>203249</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>139703</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>229361</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>73,79%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>83,27%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>238124</t>
+          <t>207557</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>206313</t>
+          <t>194777</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255426</t>
+          <t>217780</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>441372</t>
+          <t>438103</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>369011</t>
+          <t>410449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>474437</t>
+          <t>457096</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,52%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,67%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>94910</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>77347</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>124939</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>18,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>113048</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>85095</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>196712</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>105364</t>
+          <t>87580</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84499</t>
+          <t>73954</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>142608</t>
+          <t>103379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>218412</t>
+          <t>182490</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>180719</t>
+          <t>159899</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>303305</t>
+          <t>213725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>837</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>594280</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>564251</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>611843</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>86,23%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>81,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>543023</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>459359</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>570976</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>82,77%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>70,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>87,03%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>837</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>642101</t>
+          <t>533234</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>604857</t>
+          <t>517435</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>662966</t>
+          <t>546860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1185124</t>
+          <t>1127514</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1100231</t>
+          <t>1096279</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1222817</t>
+          <t>1150105</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,79%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>689190</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>921</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>656071</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>747465</t>
+          <t>620814</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1403536</t>
+          <t>1310004</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
